--- a/data/nzd0272/nzd0272.xlsx
+++ b/data/nzd0272/nzd0272.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U365"/>
+  <dimension ref="A1:U368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25639,6 +25639,213 @@
         <v>344.39</v>
       </c>
       <c r="U365" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>344.48</v>
+      </c>
+      <c r="C366" t="n">
+        <v>330.84</v>
+      </c>
+      <c r="D366" t="n">
+        <v>322.64</v>
+      </c>
+      <c r="E366" t="n">
+        <v>326.32</v>
+      </c>
+      <c r="F366" t="n">
+        <v>321.57</v>
+      </c>
+      <c r="G366" t="n">
+        <v>328.08</v>
+      </c>
+      <c r="H366" t="n">
+        <v>321.05</v>
+      </c>
+      <c r="I366" t="n">
+        <v>324.42</v>
+      </c>
+      <c r="J366" t="n">
+        <v>315.86</v>
+      </c>
+      <c r="K366" t="n">
+        <v>328.87</v>
+      </c>
+      <c r="L366" t="n">
+        <v>322.8</v>
+      </c>
+      <c r="M366" t="n">
+        <v>327.44</v>
+      </c>
+      <c r="N366" t="n">
+        <v>327.08</v>
+      </c>
+      <c r="O366" t="n">
+        <v>327.33</v>
+      </c>
+      <c r="P366" t="n">
+        <v>334.74</v>
+      </c>
+      <c r="Q366" t="n">
+        <v>334.03</v>
+      </c>
+      <c r="R366" t="n">
+        <v>338.02</v>
+      </c>
+      <c r="S366" t="n">
+        <v>337.82</v>
+      </c>
+      <c r="T366" t="n">
+        <v>344.01</v>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:55+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>343.78</v>
+      </c>
+      <c r="C367" t="n">
+        <v>329.36</v>
+      </c>
+      <c r="D367" t="n">
+        <v>321.01</v>
+      </c>
+      <c r="E367" t="n">
+        <v>325.16</v>
+      </c>
+      <c r="F367" t="n">
+        <v>321.57</v>
+      </c>
+      <c r="G367" t="n">
+        <v>327.16</v>
+      </c>
+      <c r="H367" t="n">
+        <v>321.05</v>
+      </c>
+      <c r="I367" t="n">
+        <v>323.05</v>
+      </c>
+      <c r="J367" t="n">
+        <v>312.96</v>
+      </c>
+      <c r="K367" t="n">
+        <v>326.6</v>
+      </c>
+      <c r="L367" t="n">
+        <v>320.02</v>
+      </c>
+      <c r="M367" t="n">
+        <v>326.04</v>
+      </c>
+      <c r="N367" t="n">
+        <v>326.21</v>
+      </c>
+      <c r="O367" t="n">
+        <v>325.73</v>
+      </c>
+      <c r="P367" t="n">
+        <v>333.29</v>
+      </c>
+      <c r="Q367" t="n">
+        <v>330.84</v>
+      </c>
+      <c r="R367" t="n">
+        <v>334.91</v>
+      </c>
+      <c r="S367" t="n">
+        <v>337.82</v>
+      </c>
+      <c r="T367" t="n">
+        <v>343.4</v>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:12+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>343.73</v>
+      </c>
+      <c r="C368" t="n">
+        <v>329.59</v>
+      </c>
+      <c r="D368" t="n">
+        <v>320.97</v>
+      </c>
+      <c r="E368" t="n">
+        <v>325.26</v>
+      </c>
+      <c r="F368" t="n">
+        <v>321.53</v>
+      </c>
+      <c r="G368" t="n">
+        <v>326.83</v>
+      </c>
+      <c r="H368" t="n">
+        <v>319.96</v>
+      </c>
+      <c r="I368" t="n">
+        <v>322.36</v>
+      </c>
+      <c r="J368" t="n">
+        <v>312.2</v>
+      </c>
+      <c r="K368" t="n">
+        <v>325.7</v>
+      </c>
+      <c r="L368" t="n">
+        <v>320.22</v>
+      </c>
+      <c r="M368" t="n">
+        <v>325.82</v>
+      </c>
+      <c r="N368" t="n">
+        <v>326.45</v>
+      </c>
+      <c r="O368" t="n">
+        <v>325.95</v>
+      </c>
+      <c r="P368" t="n">
+        <v>333.63</v>
+      </c>
+      <c r="Q368" t="n">
+        <v>331.67</v>
+      </c>
+      <c r="R368" t="n">
+        <v>334.12</v>
+      </c>
+      <c r="S368" t="n">
+        <v>336.34</v>
+      </c>
+      <c r="T368" t="n">
+        <v>341.5</v>
+      </c>
+      <c r="U368" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25655,7 +25862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B377"/>
+  <dimension ref="A1:B380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29428,6 +29635,36 @@
       </c>
       <c r="B377" t="n">
         <v>-0.77</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>1.04</v>
       </c>
     </row>
   </sheetData>
@@ -29596,28 +29833,28 @@
         <v>0.14</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2136405159691227</v>
+        <v>-0.2103260670551934</v>
       </c>
       <c r="J2" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K2" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06243994993449786</v>
+        <v>0.06150960608071487</v>
       </c>
       <c r="M2" t="n">
-        <v>4.929847060144857</v>
+        <v>4.906969920807398</v>
       </c>
       <c r="N2" t="n">
-        <v>37.05446877974068</v>
+        <v>36.78899584166505</v>
       </c>
       <c r="O2" t="n">
-        <v>6.087238189831303</v>
+        <v>6.065393296536099</v>
       </c>
       <c r="P2" t="n">
-        <v>347.5425656886051</v>
+        <v>347.5061025545606</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29674,28 +29911,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2805699021952676</v>
+        <v>-0.2784407098522646</v>
       </c>
       <c r="J3" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K3" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1210567091508189</v>
+        <v>0.1211041693657249</v>
       </c>
       <c r="M3" t="n">
-        <v>4.583194260604965</v>
+        <v>4.557530071625952</v>
       </c>
       <c r="N3" t="n">
-        <v>30.90231114807554</v>
+        <v>30.66822350295011</v>
       </c>
       <c r="O3" t="n">
-        <v>5.558984722777671</v>
+        <v>5.537889805959496</v>
       </c>
       <c r="P3" t="n">
-        <v>336.0208703283311</v>
+        <v>335.9974509537508</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29752,28 +29989,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1117373260321789</v>
+        <v>-0.1118045743507316</v>
       </c>
       <c r="J4" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K4" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02005540940179473</v>
+        <v>0.02039900736100009</v>
       </c>
       <c r="M4" t="n">
-        <v>4.391129594672081</v>
+        <v>4.361341384417313</v>
       </c>
       <c r="N4" t="n">
-        <v>32.98400168827592</v>
+        <v>32.719312755524</v>
       </c>
       <c r="O4" t="n">
-        <v>5.743170003428065</v>
+        <v>5.72007978576558</v>
       </c>
       <c r="P4" t="n">
-        <v>324.557335161554</v>
+        <v>324.5580846646787</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29830,28 +30067,28 @@
         <v>0.154</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1014784713669477</v>
+        <v>-0.1001277965368524</v>
       </c>
       <c r="J5" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K5" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01674409418684808</v>
+        <v>0.01656771631607945</v>
       </c>
       <c r="M5" t="n">
-        <v>4.250184219529154</v>
+        <v>4.222286274277393</v>
       </c>
       <c r="N5" t="n">
-        <v>32.69561766828547</v>
+        <v>32.43664855915652</v>
       </c>
       <c r="O5" t="n">
-        <v>5.71800819064519</v>
+        <v>5.695318126246901</v>
       </c>
       <c r="P5" t="n">
-        <v>327.4076700238131</v>
+        <v>327.3928152296066</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29908,28 +30145,28 @@
         <v>0.1369</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2893891052153972</v>
+        <v>-0.2899032628351577</v>
       </c>
       <c r="J6" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K6" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08656896186488183</v>
+        <v>0.08814889854910413</v>
       </c>
       <c r="M6" t="n">
-        <v>5.60588314493887</v>
+        <v>5.562673757070047</v>
       </c>
       <c r="N6" t="n">
-        <v>47.77654244642182</v>
+        <v>47.38687722140498</v>
       </c>
       <c r="O6" t="n">
-        <v>6.912057757746373</v>
+        <v>6.883812695113441</v>
       </c>
       <c r="P6" t="n">
-        <v>329.5879872240664</v>
+        <v>329.5936443973602</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29986,28 +30223,28 @@
         <v>0.1052</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1674368467454549</v>
+        <v>-0.1613242483460663</v>
       </c>
       <c r="J7" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K7" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03151837552744063</v>
+        <v>0.02971364733050386</v>
       </c>
       <c r="M7" t="n">
-        <v>5.477549326249974</v>
+        <v>5.466566512670616</v>
       </c>
       <c r="N7" t="n">
-        <v>46.57645602868846</v>
+        <v>46.32208564479526</v>
       </c>
       <c r="O7" t="n">
-        <v>6.82469457402223</v>
+        <v>6.806033032890397</v>
       </c>
       <c r="P7" t="n">
-        <v>327.8649675628749</v>
+        <v>327.7977205654078</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30064,28 +30301,28 @@
         <v>0.0635</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.07305209495689688</v>
+        <v>-0.06667788905697868</v>
       </c>
       <c r="J8" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K8" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004938276741287884</v>
+        <v>0.004174710888153021</v>
       </c>
       <c r="M8" t="n">
-        <v>6.062094001758106</v>
+        <v>6.041402133543587</v>
       </c>
       <c r="N8" t="n">
-        <v>58.34308897390074</v>
+        <v>58.0014842163167</v>
       </c>
       <c r="O8" t="n">
-        <v>7.638264788150561</v>
+        <v>7.615870548815591</v>
       </c>
       <c r="P8" t="n">
-        <v>318.5128645837798</v>
+        <v>318.4427755150348</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30142,28 +30379,28 @@
         <v>0.0706</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2414612151707486</v>
+        <v>-0.2292366114366879</v>
       </c>
       <c r="J9" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K9" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05954288740456704</v>
+        <v>0.0542958833862367</v>
       </c>
       <c r="M9" t="n">
-        <v>5.577635946243142</v>
+        <v>5.596383176118827</v>
       </c>
       <c r="N9" t="n">
-        <v>49.96355605478096</v>
+        <v>50.05817504303525</v>
       </c>
       <c r="O9" t="n">
-        <v>7.068490366038632</v>
+        <v>7.075180212760325</v>
       </c>
       <c r="P9" t="n">
-        <v>321.811042040364</v>
+        <v>321.6766233069695</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30220,28 +30457,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1313013821115892</v>
+        <v>-0.1341095331486595</v>
       </c>
       <c r="J10" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K10" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01409579512072368</v>
+        <v>0.01492337462442161</v>
       </c>
       <c r="M10" t="n">
-        <v>6.742463410476364</v>
+        <v>6.706811439305711</v>
       </c>
       <c r="N10" t="n">
-        <v>65.1959387601369</v>
+        <v>64.70936232345531</v>
       </c>
       <c r="O10" t="n">
-        <v>8.074400210550435</v>
+        <v>8.044212971040443</v>
       </c>
       <c r="P10" t="n">
-        <v>318.976119739659</v>
+        <v>319.0070376624006</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30298,28 +30535,28 @@
         <v>0.0951</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1253903693130641</v>
+        <v>-0.1165385950177623</v>
       </c>
       <c r="J11" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K11" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02278013105920418</v>
+        <v>0.01990799987791436</v>
       </c>
       <c r="M11" t="n">
-        <v>4.82846514936161</v>
+        <v>4.836506546929125</v>
       </c>
       <c r="N11" t="n">
-        <v>36.4671010923102</v>
+        <v>36.44379683981647</v>
       </c>
       <c r="O11" t="n">
-        <v>6.038799640020375</v>
+        <v>6.036869788211145</v>
       </c>
       <c r="P11" t="n">
-        <v>324.6777894183329</v>
+        <v>324.5804155656429</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30376,28 +30613,28 @@
         <v>0.1377</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.02668077077718591</v>
+        <v>-0.02080356227041437</v>
       </c>
       <c r="J12" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K12" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001068783402955242</v>
+        <v>0.0006583634504665481</v>
       </c>
       <c r="M12" t="n">
-        <v>4.683711030901661</v>
+        <v>4.676941639737017</v>
       </c>
       <c r="N12" t="n">
-        <v>35.97323006045382</v>
+        <v>35.80704895128189</v>
       </c>
       <c r="O12" t="n">
-        <v>5.99776875683398</v>
+        <v>5.983899142806627</v>
       </c>
       <c r="P12" t="n">
-        <v>317.93341231453</v>
+        <v>317.8687629186543</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30454,28 +30691,28 @@
         <v>0.1966</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.07547028777554338</v>
+        <v>-0.0716052832688153</v>
       </c>
       <c r="J13" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K13" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0183264289516607</v>
+        <v>0.01674031899095418</v>
       </c>
       <c r="M13" t="n">
-        <v>3.14411231620236</v>
+        <v>3.141640204678644</v>
       </c>
       <c r="N13" t="n">
-        <v>16.49597809310391</v>
+        <v>16.41494689854726</v>
       </c>
       <c r="O13" t="n">
-        <v>4.061524109629772</v>
+        <v>4.05153636273294</v>
       </c>
       <c r="P13" t="n">
-        <v>325.9447477138575</v>
+        <v>325.9022321125672</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30532,28 +30769,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.003218051334295138</v>
+        <v>-0.002363177599676711</v>
       </c>
       <c r="J14" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K14" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L14" t="n">
-        <v>4.78106075028073e-05</v>
+        <v>2.619877563081463e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>2.490553135096551</v>
+        <v>2.475201280110008</v>
       </c>
       <c r="N14" t="n">
-        <v>11.71056143237017</v>
+        <v>11.61836979050624</v>
       </c>
       <c r="O14" t="n">
-        <v>3.422069758548206</v>
+        <v>3.408572984476971</v>
       </c>
       <c r="P14" t="n">
-        <v>326.1138798698016</v>
+        <v>326.1044776871029</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30610,28 +30847,28 @@
         <v>0.1851</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.00216812876354378</v>
+        <v>0.001389210639449598</v>
       </c>
       <c r="J15" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K15" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L15" t="n">
-        <v>1.498742265593211e-05</v>
+        <v>6.237057692093373e-06</v>
       </c>
       <c r="M15" t="n">
-        <v>3.03936217068433</v>
+        <v>3.035786079238977</v>
       </c>
       <c r="N15" t="n">
-        <v>16.95795529408482</v>
+        <v>16.86547501801084</v>
       </c>
       <c r="O15" t="n">
-        <v>4.118003799668575</v>
+        <v>4.106759673758721</v>
       </c>
       <c r="P15" t="n">
-        <v>324.101392601155</v>
+        <v>324.0622607411397</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30688,28 +30925,28 @@
         <v>0.1676</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.08924129791469461</v>
+        <v>-0.08741253037964183</v>
       </c>
       <c r="J16" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K16" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02033517120156481</v>
+        <v>0.0198271818285084</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45932765440891</v>
+        <v>3.440389826010421</v>
       </c>
       <c r="N16" t="n">
-        <v>20.74427434018601</v>
+        <v>20.58893562571365</v>
       </c>
       <c r="O16" t="n">
-        <v>4.554588273399255</v>
+        <v>4.537503236992085</v>
       </c>
       <c r="P16" t="n">
-        <v>335.0803801346688</v>
+        <v>335.0602653726177</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30766,28 +31003,28 @@
         <v>0.1225</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.01447662404961482</v>
+        <v>-0.01038995370827682</v>
       </c>
       <c r="J17" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K17" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0003094622857561236</v>
+        <v>0.000161731917511676</v>
       </c>
       <c r="M17" t="n">
-        <v>4.66177564893507</v>
+        <v>4.645549759437682</v>
       </c>
       <c r="N17" t="n">
-        <v>36.60405948960531</v>
+        <v>36.37525870089308</v>
       </c>
       <c r="O17" t="n">
-        <v>6.050128882065679</v>
+        <v>6.031190487863327</v>
       </c>
       <c r="P17" t="n">
-        <v>329.9257071066123</v>
+        <v>329.8807568994902</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30844,28 +31081,28 @@
         <v>0.1341</v>
       </c>
       <c r="I18" t="n">
-        <v>0.09650669590536806</v>
+        <v>0.1075876730044817</v>
       </c>
       <c r="J18" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K18" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01442254203095983</v>
+        <v>0.01792771285899886</v>
       </c>
       <c r="M18" t="n">
-        <v>4.666501681986913</v>
+        <v>4.688858310664527</v>
       </c>
       <c r="N18" t="n">
-        <v>34.41126595937007</v>
+        <v>34.56117054439527</v>
       </c>
       <c r="O18" t="n">
-        <v>5.866111655890133</v>
+        <v>5.878874938659205</v>
       </c>
       <c r="P18" t="n">
-        <v>325.9634936362353</v>
+        <v>325.8415971577766</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30922,28 +31159,28 @@
         <v>0.11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1977342724835539</v>
+        <v>0.2085050312467682</v>
       </c>
       <c r="J19" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K19" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03907971963318346</v>
+        <v>0.04362808687742048</v>
       </c>
       <c r="M19" t="n">
-        <v>5.937308031599542</v>
+        <v>5.946227219992952</v>
       </c>
       <c r="N19" t="n">
-        <v>51.98004228748277</v>
+        <v>51.94438012799569</v>
       </c>
       <c r="O19" t="n">
-        <v>7.20971859974318</v>
+        <v>7.207244974884348</v>
       </c>
       <c r="P19" t="n">
-        <v>325.1189540166563</v>
+        <v>325.0004567615493</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31000,28 +31237,28 @@
         <v>0.0745</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.005436763103660187</v>
+        <v>0.01535744535500557</v>
       </c>
       <c r="J20" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="K20" t="n">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="L20" t="n">
-        <v>2.194151454815163e-05</v>
+        <v>0.0001744450205330983</v>
       </c>
       <c r="M20" t="n">
-        <v>6.816457878373106</v>
+        <v>6.85847393072157</v>
       </c>
       <c r="N20" t="n">
-        <v>72.37303650374938</v>
+        <v>73.21300014384208</v>
       </c>
       <c r="O20" t="n">
-        <v>8.507234362808479</v>
+        <v>8.556459556606464</v>
       </c>
       <c r="P20" t="n">
-        <v>329.7724873755402</v>
+        <v>329.5426429550768</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31059,7 +31296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U365"/>
+  <dimension ref="A1:U368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70097,6 +70334,327 @@
         </is>
       </c>
     </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>-38.724796938759894,174.60872258921233</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>-38.72408909489892,174.60883075923127</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>-38.72338444572782,174.60887649427582</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>-38.72268678140919,174.60878588856386</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>-38.72198414899604,174.6087920282821</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>-38.7212881364259,174.60866894585655</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>-38.72058926106036,174.60870152209964</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>-38.71991438666552,174.6086433743121</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>-38.71924296903626,174.60883512091675</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>-38.71853494866537,174.6087818911887</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>-38.71784323373829,174.6089470966504</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>-38.717142355647816,174.60898969137412</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>-38.716445745436175,174.6090895271844</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>-38.71574869033033,174.60918236683713</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>-38.715046402403345,174.6091936752314</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>-38.71435180093063,174.6093062574205</t>
+        </is>
+      </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>-38.71365186794086,174.60936524541296</t>
+        </is>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>-38.71295588439457,174.60947215121092</t>
+        </is>
+      </c>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>-38.71225386064405,174.60950598151337</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:55+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>-38.72479652679922,174.60873062288775</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>-38.72408822388043,174.6088477445468</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>-38.723383486423415,174.6088952008914</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>-38.722686098724935,174.60879920111915</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>-38.72198414899604,174.6087920282821</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>-38.72128759499778,174.6086795038855</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>-38.72058926106036,174.60870152209964</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>-38.71991477091651,174.60865912230528</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>-38.71924544833799,174.60886832144496</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>-38.71853688938472,174.6088078789292</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>-38.71784561044678,174.6089789227417</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>-38.71714355255389,174.60900571874492</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>-38.716446489224055,174.60909948695397</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>-38.71575006286317,174.60920068290991</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>-38.71504771100983,174.60921026589747</t>
+        </is>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>-38.71435481293637,174.60934273903266</t>
+        </is>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>-38.713654804409664,174.60940081177824</t>
+        </is>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>-38.71295588439457,174.60947215121092</t>
+        </is>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>-38.71225443660653,174.60951295741668</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:12+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>-38.72479649737345,174.60873119672172</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>-38.724088359241584,174.608845104937</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>-38.72338346288217,174.60889565994944</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>-38.7226861575771,174.60879805348512</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>-38.721984125455215,174.60879248733121</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>-38.72128740078965,174.60868329100452</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>-38.720588778585196,174.6087140425804</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>-38.719914964443575,174.60866705377634</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>-38.71924609808447,174.60887702227336</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>-38.71853765883131,174.608818182439</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>-38.71784543946084,174.60897663309478</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>-38.717143740638924,174.6090082373318</t>
+        </is>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>-38.716446284041275,174.60909673943132</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>-38.71574987414007,174.60919816444988</t>
+        </is>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>-38.71504740416438,174.6092063756723</t>
+        </is>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>-38.71435402924947,174.6093332469515</t>
+        </is>
+      </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>-38.713655550327665,174.60940984632157</t>
+        </is>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>-38.71295728180775,174.60948907651974</t>
+        </is>
+      </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>-38.71225623058533,174.60953468564068</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0272/nzd0272.xlsx
+++ b/data/nzd0272/nzd0272.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U368"/>
+  <dimension ref="A1:U369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25848,6 +25848,75 @@
       <c r="U368" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>345.71</v>
+      </c>
+      <c r="C369" t="n">
+        <v>328.79</v>
+      </c>
+      <c r="D369" t="n">
+        <v>320.19</v>
+      </c>
+      <c r="E369" t="n">
+        <v>325.1</v>
+      </c>
+      <c r="F369" t="n">
+        <v>320.96</v>
+      </c>
+      <c r="G369" t="n">
+        <v>327.38</v>
+      </c>
+      <c r="H369" t="n">
+        <v>319.67</v>
+      </c>
+      <c r="I369" t="n">
+        <v>323.74</v>
+      </c>
+      <c r="J369" t="n">
+        <v>312.2</v>
+      </c>
+      <c r="K369" t="n">
+        <v>327.67</v>
+      </c>
+      <c r="L369" t="n">
+        <v>322.75</v>
+      </c>
+      <c r="M369" t="n">
+        <v>324.71</v>
+      </c>
+      <c r="N369" t="n">
+        <v>327.11</v>
+      </c>
+      <c r="O369" t="n">
+        <v>325.73</v>
+      </c>
+      <c r="P369" t="n">
+        <v>333.63</v>
+      </c>
+      <c r="Q369" t="n">
+        <v>333.35</v>
+      </c>
+      <c r="R369" t="n">
+        <v>336.05</v>
+      </c>
+      <c r="S369" t="n">
+        <v>338.48</v>
+      </c>
+      <c r="T369" t="n">
+        <v>341.77</v>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -25862,7 +25931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B380"/>
+  <dimension ref="A1:B381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29665,6 +29734,16 @@
       </c>
       <c r="B380" t="n">
         <v>1.04</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>-0.87</v>
       </c>
     </row>
   </sheetData>
@@ -29833,28 +29912,28 @@
         <v>0.14</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2103260670551934</v>
+        <v>-0.2083622899716913</v>
       </c>
       <c r="J2" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K2" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06150960608071487</v>
+        <v>0.06067939665210742</v>
       </c>
       <c r="M2" t="n">
-        <v>4.906969920807398</v>
+        <v>4.903896809306793</v>
       </c>
       <c r="N2" t="n">
-        <v>36.78899584166505</v>
+        <v>36.72826302425895</v>
       </c>
       <c r="O2" t="n">
-        <v>6.065393296536099</v>
+        <v>6.060384725762792</v>
       </c>
       <c r="P2" t="n">
-        <v>347.5061025545606</v>
+        <v>347.4844522881795</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29911,28 +29990,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2784407098522646</v>
+        <v>-0.2783294022462774</v>
       </c>
       <c r="J3" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K3" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1211041693657249</v>
+        <v>0.1215896269507331</v>
       </c>
       <c r="M3" t="n">
-        <v>4.557530071625952</v>
+        <v>4.545757555437105</v>
       </c>
       <c r="N3" t="n">
-        <v>30.66822350295011</v>
+        <v>30.58501199528084</v>
       </c>
       <c r="O3" t="n">
-        <v>5.537889805959496</v>
+        <v>5.530371777311254</v>
       </c>
       <c r="P3" t="n">
-        <v>335.9974509537508</v>
+        <v>335.9962238087047</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29989,28 +30068,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1118045743507316</v>
+        <v>-0.1125210646822462</v>
       </c>
       <c r="J4" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K4" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02039900736100009</v>
+        <v>0.02076126774560183</v>
       </c>
       <c r="M4" t="n">
-        <v>4.361341384417313</v>
+        <v>4.353376445224561</v>
       </c>
       <c r="N4" t="n">
-        <v>32.719312755524</v>
+        <v>32.63562476189295</v>
       </c>
       <c r="O4" t="n">
-        <v>5.72007978576558</v>
+        <v>5.712759820077591</v>
       </c>
       <c r="P4" t="n">
-        <v>324.5580846646787</v>
+        <v>324.5659838334118</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30067,28 +30146,28 @@
         <v>0.154</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1001277965368524</v>
+        <v>-0.09993503868936103</v>
       </c>
       <c r="J5" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K5" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01656771631607945</v>
+        <v>0.01659203092667039</v>
       </c>
       <c r="M5" t="n">
-        <v>4.222286274277393</v>
+        <v>4.211781037259835</v>
       </c>
       <c r="N5" t="n">
-        <v>32.43664855915652</v>
+        <v>32.34888353320271</v>
       </c>
       <c r="O5" t="n">
-        <v>5.695318126246901</v>
+        <v>5.687607892005452</v>
       </c>
       <c r="P5" t="n">
-        <v>327.3928152296066</v>
+        <v>327.3906901112414</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30145,28 +30224,28 @@
         <v>0.1369</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2899032628351577</v>
+        <v>-0.290367286516761</v>
       </c>
       <c r="J6" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K6" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08814889854910413</v>
+        <v>0.08883525696838956</v>
       </c>
       <c r="M6" t="n">
-        <v>5.562673757070047</v>
+        <v>5.54990204292373</v>
       </c>
       <c r="N6" t="n">
-        <v>47.38687722140498</v>
+        <v>47.26029929333562</v>
       </c>
       <c r="O6" t="n">
-        <v>6.883812695113441</v>
+        <v>6.874612664967795</v>
       </c>
       <c r="P6" t="n">
-        <v>329.5936443973602</v>
+        <v>329.5987601696127</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30223,28 +30302,28 @@
         <v>0.1052</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1613242483460663</v>
+        <v>-0.1593233072372365</v>
       </c>
       <c r="J7" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K7" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02971364733050386</v>
+        <v>0.0291286732451993</v>
       </c>
       <c r="M7" t="n">
-        <v>5.466566512670616</v>
+        <v>5.462697248216799</v>
       </c>
       <c r="N7" t="n">
-        <v>46.32208564479526</v>
+        <v>46.23694685758856</v>
       </c>
       <c r="O7" t="n">
-        <v>6.806033032890397</v>
+        <v>6.799775500528569</v>
       </c>
       <c r="P7" t="n">
-        <v>327.7977205654078</v>
+        <v>327.7756605727625</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30301,28 +30380,28 @@
         <v>0.0635</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.06667788905697868</v>
+        <v>-0.06512956525288166</v>
       </c>
       <c r="J8" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K8" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004174710888153021</v>
+        <v>0.004003406382544705</v>
       </c>
       <c r="M8" t="n">
-        <v>6.041402133543587</v>
+        <v>6.031947451828706</v>
       </c>
       <c r="N8" t="n">
-        <v>58.0014842163167</v>
+        <v>57.86755101259604</v>
       </c>
       <c r="O8" t="n">
-        <v>7.615870548815591</v>
+        <v>7.6070724337682</v>
       </c>
       <c r="P8" t="n">
-        <v>318.4427755150348</v>
+        <v>318.4257142790601</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30379,28 +30458,28 @@
         <v>0.0706</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2292366114366879</v>
+        <v>-0.225031665128909</v>
       </c>
       <c r="J9" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K9" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0542958833862367</v>
+        <v>0.05251135882735292</v>
       </c>
       <c r="M9" t="n">
-        <v>5.596383176118827</v>
+        <v>5.603629662033009</v>
       </c>
       <c r="N9" t="n">
-        <v>50.05817504303525</v>
+        <v>50.10240716285439</v>
       </c>
       <c r="O9" t="n">
-        <v>7.075180212760325</v>
+        <v>7.078305387792645</v>
       </c>
       <c r="P9" t="n">
-        <v>321.6766233069695</v>
+        <v>321.6302883084197</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30457,28 +30536,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1341095331486595</v>
+        <v>-0.1357732137587619</v>
       </c>
       <c r="J10" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K10" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01492337462442161</v>
+        <v>0.01536449867191947</v>
       </c>
       <c r="M10" t="n">
-        <v>6.706811439305711</v>
+        <v>6.698855518879765</v>
       </c>
       <c r="N10" t="n">
-        <v>64.70936232345531</v>
+        <v>64.56168307709034</v>
       </c>
       <c r="O10" t="n">
-        <v>8.044212971040443</v>
+        <v>8.035028505057735</v>
       </c>
       <c r="P10" t="n">
-        <v>319.0070376624006</v>
+        <v>319.025379422616</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30535,28 +30614,28 @@
         <v>0.0951</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1165385950177623</v>
+        <v>-0.1133480304610581</v>
       </c>
       <c r="J11" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K11" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01990799987791436</v>
+        <v>0.0188996261473483</v>
       </c>
       <c r="M11" t="n">
-        <v>4.836506546929125</v>
+        <v>4.84035807476511</v>
       </c>
       <c r="N11" t="n">
-        <v>36.44379683981647</v>
+        <v>36.44833850703981</v>
       </c>
       <c r="O11" t="n">
-        <v>6.036869788211145</v>
+        <v>6.037245937266413</v>
       </c>
       <c r="P11" t="n">
-        <v>324.5804155656429</v>
+        <v>324.5452402022377</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -30613,28 +30692,28 @@
         <v>0.1377</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.02080356227041437</v>
+        <v>-0.01800663881730091</v>
       </c>
       <c r="J12" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K12" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0006583634504665481</v>
+        <v>0.0004948643802523689</v>
       </c>
       <c r="M12" t="n">
-        <v>4.676941639737017</v>
+        <v>4.67951513977209</v>
       </c>
       <c r="N12" t="n">
-        <v>35.80704895128189</v>
+        <v>35.78934033539178</v>
       </c>
       <c r="O12" t="n">
-        <v>5.983899142806627</v>
+        <v>5.982419271113633</v>
       </c>
       <c r="P12" t="n">
-        <v>317.8687629186543</v>
+        <v>317.8379273730538</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -30691,28 +30770,28 @@
         <v>0.1966</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0716052832688153</v>
+        <v>-0.07123651340912546</v>
       </c>
       <c r="J13" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K13" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01674031899095418</v>
+        <v>0.01665732713159429</v>
       </c>
       <c r="M13" t="n">
-        <v>3.141640204678644</v>
+        <v>3.135320494408862</v>
       </c>
       <c r="N13" t="n">
-        <v>16.41494689854726</v>
+        <v>16.37172471173842</v>
       </c>
       <c r="O13" t="n">
-        <v>4.05153636273294</v>
+        <v>4.046198797851932</v>
       </c>
       <c r="P13" t="n">
-        <v>325.9022321125672</v>
+        <v>325.898166495465</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -30769,28 +30848,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.002363177599676711</v>
+        <v>-0.001811484109312248</v>
       </c>
       <c r="J14" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K14" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L14" t="n">
-        <v>2.619877563081463e-05</v>
+        <v>1.547292395231992e-05</v>
       </c>
       <c r="M14" t="n">
-        <v>2.475201280110008</v>
+        <v>2.471681492929656</v>
       </c>
       <c r="N14" t="n">
-        <v>11.61836979050624</v>
+        <v>11.58989491263869</v>
       </c>
       <c r="O14" t="n">
-        <v>3.408572984476971</v>
+        <v>3.404393472064986</v>
       </c>
       <c r="P14" t="n">
-        <v>326.1044776871029</v>
+        <v>326.0983953719932</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -30847,28 +30926,28 @@
         <v>0.1851</v>
       </c>
       <c r="I15" t="n">
-        <v>0.001389210639449598</v>
+        <v>0.002229843669859492</v>
       </c>
       <c r="J15" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K15" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L15" t="n">
-        <v>6.237057692093373e-06</v>
+        <v>1.614837916208423e-05</v>
       </c>
       <c r="M15" t="n">
-        <v>3.035786079238977</v>
+        <v>3.032604302380568</v>
       </c>
       <c r="N15" t="n">
-        <v>16.86547501801084</v>
+        <v>16.82683489849478</v>
       </c>
       <c r="O15" t="n">
-        <v>4.106759673758721</v>
+        <v>4.102052522639706</v>
       </c>
       <c r="P15" t="n">
-        <v>324.0622607411397</v>
+        <v>324.0529929229182</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30925,28 +31004,28 @@
         <v>0.1676</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.08741253037964183</v>
+        <v>-0.08694734446024047</v>
       </c>
       <c r="J16" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K16" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0198271818285084</v>
+        <v>0.01972207967802597</v>
       </c>
       <c r="M16" t="n">
-        <v>3.440389826010421</v>
+        <v>3.433413505843575</v>
       </c>
       <c r="N16" t="n">
-        <v>20.58893562571365</v>
+        <v>20.53518917922599</v>
       </c>
       <c r="O16" t="n">
-        <v>4.537503236992085</v>
+        <v>4.531576897640157</v>
       </c>
       <c r="P16" t="n">
-        <v>335.0602653726177</v>
+        <v>335.055136786916</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31003,28 +31082,28 @@
         <v>0.1225</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.01038995370827682</v>
+        <v>-0.008463885039710441</v>
       </c>
       <c r="J17" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K17" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L17" t="n">
-        <v>0.000161731917511676</v>
+        <v>0.0001077968994391831</v>
       </c>
       <c r="M17" t="n">
-        <v>4.645549759437682</v>
+        <v>4.643162776610397</v>
       </c>
       <c r="N17" t="n">
-        <v>36.37525870089308</v>
+        <v>36.31415776941793</v>
       </c>
       <c r="O17" t="n">
-        <v>6.031190487863327</v>
+        <v>6.026122946755893</v>
       </c>
       <c r="P17" t="n">
-        <v>329.8807568994902</v>
+        <v>329.8595223611645</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31081,28 +31160,28 @@
         <v>0.1341</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1075876730044817</v>
+        <v>0.1113646727646403</v>
       </c>
       <c r="J18" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K18" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01792771285899886</v>
+        <v>0.01920572179969748</v>
       </c>
       <c r="M18" t="n">
-        <v>4.688858310664527</v>
+        <v>4.696590784593075</v>
       </c>
       <c r="N18" t="n">
-        <v>34.56117054439527</v>
+        <v>34.61240144332688</v>
       </c>
       <c r="O18" t="n">
-        <v>5.878874938659205</v>
+        <v>5.883230527807565</v>
       </c>
       <c r="P18" t="n">
-        <v>325.8415971577766</v>
+        <v>325.7999564585263</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31159,28 +31238,28 @@
         <v>0.11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2085050312467682</v>
+        <v>0.2125800858765185</v>
       </c>
       <c r="J19" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K19" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L19" t="n">
-        <v>0.04362808687742048</v>
+        <v>0.04536302185357466</v>
       </c>
       <c r="M19" t="n">
-        <v>5.946227219992952</v>
+        <v>5.952045213217906</v>
       </c>
       <c r="N19" t="n">
-        <v>51.94438012799569</v>
+        <v>51.97218594376431</v>
       </c>
       <c r="O19" t="n">
-        <v>7.207244974884348</v>
+        <v>7.209173735163018</v>
       </c>
       <c r="P19" t="n">
-        <v>325.0004567615493</v>
+        <v>324.9555300644242</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31237,28 +31316,28 @@
         <v>0.0745</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01535744535500557</v>
+        <v>0.02147487382451959</v>
       </c>
       <c r="J20" t="n">
+        <v>368</v>
+      </c>
+      <c r="K20" t="n">
         <v>367</v>
       </c>
-      <c r="K20" t="n">
-        <v>366</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.0001744450205330983</v>
+        <v>0.000341114625478256</v>
       </c>
       <c r="M20" t="n">
-        <v>6.85847393072157</v>
+        <v>6.868375103854577</v>
       </c>
       <c r="N20" t="n">
-        <v>73.21300014384208</v>
+        <v>73.39110607327619</v>
       </c>
       <c r="O20" t="n">
-        <v>8.556459556606464</v>
+        <v>8.56686092295633</v>
       </c>
       <c r="P20" t="n">
-        <v>329.5426429550768</v>
+        <v>329.4748847138954</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31296,7 +31375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U368"/>
+  <dimension ref="A1:U369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70655,6 +70734,113 @@
         </is>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>-38.7247976626323,174.6087084728967</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>-38.72408788841995,174.60885428618846</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>-38.72338300382745,174.6089046115812</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>-38.72268606341365,174.6087998896996</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>-38.72198378999827,174.6087990287814</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>-38.72128772446982,174.60867697913946</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>-38.72058865022002,174.60871737371747</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>-38.71991457738891,174.60865119083422</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>-38.71924609808447,174.60887702227336</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>-38.71853597459703,174.60879562920115</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>-38.71784327648492,174.6089476690621</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>-38.71714468961261,174.6090209447476</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>-38.71644571978831,174.6090891837441</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>-38.71575006286317,174.60920068290991</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>-38.71504740416438,174.6092063756723</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>-38.714352442989245,174.60931403406488</t>
+        </is>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>-38.71365372802045,174.60938777458938</t>
+        </is>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>-38.712955261223016,174.60946460343825</t>
+        </is>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>-38.71225597565174,174.60953159794565</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
